--- a/input/timetable/Физическая культура_.xlsx
+++ b/input/timetable/Физическая культура_.xlsx
@@ -341,7 +341,7 @@
     <t xml:space="preserve">Психология физической культуры (лек), К202// </t>
   </si>
   <si>
-    <t>Физиология человека (пр), А410//</t>
+    <t>Физиология человека (пр), А431//</t>
   </si>
 </sst>
 </file>
@@ -1369,130 +1369,6 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1550,45 +1426,160 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1598,14 +1589,20 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1634,59 +1631,53 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1697,30 +1688,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1784,32 +1751,53 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1819,17 +1807,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1843,6 +1820,29 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
@@ -2271,12 +2271,12 @@
       <c r="A8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="100" t="s">
+      <c r="C8" s="97" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
@@ -2299,58 +2299,58 @@
       <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="105" t="s">
+      <c r="C10" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="106"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="107"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="105"/>
+      <c r="F10" s="106"/>
     </row>
     <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="25"/>
       <c r="B11" s="26">
         <v>2</v>
       </c>
-      <c r="C11" s="108" t="s">
+      <c r="C11" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="109"/>
-      <c r="E11" s="109"/>
-      <c r="F11" s="110"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="109"/>
     </row>
     <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
       <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="102" t="s">
+      <c r="C12" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="104"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="103"/>
     </row>
     <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="25"/>
       <c r="B13" s="26">
         <v>4</v>
       </c>
-      <c r="C13" s="102" t="s">
+      <c r="C13" s="101" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="103"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="104"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="103"/>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="27"/>
       <c r="B14" s="28">
         <v>5</v>
       </c>
-      <c r="C14" s="111"/>
-      <c r="D14" s="112"/>
-      <c r="E14" s="112"/>
-      <c r="F14" s="113"/>
+      <c r="C14" s="110"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="112"/>
     </row>
     <row r="15" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="29" t="s">
@@ -2359,42 +2359,42 @@
       <c r="B15" s="30">
         <v>1</v>
       </c>
-      <c r="C15" s="114" t="s">
+      <c r="C15" s="113" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="116"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="115"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
       <c r="B16" s="26">
         <v>2</v>
       </c>
-      <c r="C16" s="117"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="119"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="118"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A17" s="25"/>
       <c r="B17" s="26">
         <v>3</v>
       </c>
-      <c r="C17" s="120" t="s">
+      <c r="C17" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="122"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="120"/>
+      <c r="F17" s="121"/>
     </row>
     <row r="18" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="31"/>
       <c r="B18" s="28"/>
-      <c r="C18" s="123"/>
-      <c r="D18" s="124"/>
-      <c r="E18" s="124"/>
-      <c r="F18" s="125"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="123"/>
+      <c r="F18" s="124"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A19" s="29" t="s">
@@ -2403,42 +2403,42 @@
       <c r="B19" s="30">
         <v>1</v>
       </c>
-      <c r="C19" s="101" t="s">
+      <c r="C19" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="89"/>
-      <c r="E19" s="89"/>
-      <c r="F19" s="90"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="100"/>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.4">
       <c r="A20" s="25"/>
       <c r="B20" s="26">
         <v>2</v>
       </c>
-      <c r="C20" s="129"/>
-      <c r="D20" s="130"/>
-      <c r="E20" s="130"/>
-      <c r="F20" s="131"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="75"/>
     </row>
     <row r="21" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="25"/>
       <c r="B21" s="26">
         <v>3</v>
       </c>
-      <c r="C21" s="132" t="s">
+      <c r="C21" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="133"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="134"/>
+      <c r="D21" s="77"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="78"/>
     </row>
     <row r="22" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="31"/>
       <c r="B22" s="28"/>
-      <c r="C22" s="144"/>
-      <c r="D22" s="145"/>
-      <c r="E22" s="145"/>
-      <c r="F22" s="146"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="90"/>
     </row>
     <row r="23" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="29" t="s">
@@ -2447,58 +2447,58 @@
       <c r="B23" s="30">
         <v>1</v>
       </c>
-      <c r="C23" s="135" t="s">
+      <c r="C23" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="136"/>
-      <c r="E23" s="136"/>
-      <c r="F23" s="137"/>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="81"/>
     </row>
     <row r="24" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="25"/>
       <c r="B24" s="26">
         <v>2</v>
       </c>
-      <c r="C24" s="79" t="s">
+      <c r="C24" s="94" t="s">
         <v>81</v>
       </c>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="81"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="96"/>
     </row>
     <row r="25" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="25"/>
       <c r="B25" s="26">
         <v>3</v>
       </c>
-      <c r="C25" s="147" t="s">
+      <c r="C25" s="91" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="148"/>
-      <c r="E25" s="148"/>
-      <c r="F25" s="149"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="92"/>
+      <c r="F25" s="93"/>
     </row>
     <row r="26" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="25"/>
       <c r="B26" s="26">
         <v>4</v>
       </c>
-      <c r="C26" s="138"/>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="140"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="83"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="84"/>
     </row>
     <row r="27" spans="1:20" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="31"/>
       <c r="B27" s="28">
         <v>5</v>
       </c>
-      <c r="C27" s="141" t="s">
+      <c r="C27" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="142"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="143"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="87"/>
     </row>
     <row r="28" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="29" t="s">
@@ -2507,44 +2507,44 @@
       <c r="B28" s="30">
         <v>1</v>
       </c>
-      <c r="C28" s="76" t="s">
+      <c r="C28" s="128" t="s">
         <v>105</v>
       </c>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="78"/>
+      <c r="D28" s="129"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="130"/>
     </row>
     <row r="29" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="25"/>
       <c r="B29" s="24">
         <v>2</v>
       </c>
-      <c r="C29" s="91"/>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
-      <c r="F29" s="93"/>
+      <c r="C29" s="138"/>
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="140"/>
     </row>
     <row r="30" spans="1:20" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="34"/>
       <c r="B30" s="26">
         <v>3</v>
       </c>
-      <c r="C30" s="85" t="s">
+      <c r="C30" s="134" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="87"/>
+      <c r="D30" s="135"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="136"/>
     </row>
     <row r="31" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="34"/>
       <c r="B31" s="26">
         <v>4</v>
       </c>
-      <c r="C31" s="91"/>
-      <c r="D31" s="92"/>
-      <c r="E31" s="92"/>
-      <c r="F31" s="93"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="140"/>
       <c r="T31" s="59"/>
     </row>
     <row r="32" spans="1:20" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -2552,10 +2552,10 @@
       <c r="B32" s="36">
         <v>5</v>
       </c>
-      <c r="C32" s="94"/>
-      <c r="D32" s="95"/>
-      <c r="E32" s="95"/>
-      <c r="F32" s="96"/>
+      <c r="C32" s="141"/>
+      <c r="D32" s="142"/>
+      <c r="E32" s="142"/>
+      <c r="F32" s="143"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="37" t="s">
@@ -2564,94 +2564,94 @@
       <c r="B33" s="30">
         <v>1</v>
       </c>
-      <c r="C33" s="88" t="s">
+      <c r="C33" s="137" t="s">
         <v>35</v>
       </c>
-      <c r="D33" s="89"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="90"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="99"/>
+      <c r="F33" s="100"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="38"/>
       <c r="B34" s="26">
         <v>3</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="134" t="s">
         <v>101</v>
       </c>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="87"/>
+      <c r="D34" s="135"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="136"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="39"/>
       <c r="B35" s="33">
         <v>4</v>
       </c>
-      <c r="C35" s="85" t="s">
+      <c r="C35" s="134" t="s">
         <v>83</v>
       </c>
-      <c r="D35" s="86"/>
-      <c r="E35" s="86" t="s">
+      <c r="D35" s="135"/>
+      <c r="E35" s="135" t="s">
         <v>84</v>
       </c>
-      <c r="F35" s="87"/>
+      <c r="F35" s="136"/>
     </row>
     <row r="36" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="40"/>
       <c r="B36" s="28">
         <v>5</v>
       </c>
-      <c r="C36" s="126" t="s">
+      <c r="C36" s="147" t="s">
         <v>103</v>
       </c>
-      <c r="D36" s="127"/>
-      <c r="E36" s="127"/>
-      <c r="F36" s="128"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="148"/>
+      <c r="F36" s="149"/>
     </row>
     <row r="37" spans="1:6" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="41"/>
       <c r="B37" s="42"/>
-      <c r="C37" s="82"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="84"/>
+      <c r="C37" s="131"/>
+      <c r="D37" s="132"/>
+      <c r="E37" s="132"/>
+      <c r="F37" s="133"/>
     </row>
     <row r="38" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="43"/>
       <c r="B38" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C38" s="97" t="s">
+      <c r="C38" s="144" t="s">
         <v>56</v>
       </c>
-      <c r="D38" s="98"/>
-      <c r="E38" s="98"/>
-      <c r="F38" s="99"/>
+      <c r="D38" s="145"/>
+      <c r="E38" s="145"/>
+      <c r="F38" s="146"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="44"/>
       <c r="B39" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="79" t="s">
+      <c r="C39" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="80"/>
-      <c r="E39" s="80"/>
-      <c r="F39" s="81"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="95"/>
+      <c r="F39" s="96"/>
     </row>
     <row r="40" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A40" s="46"/>
       <c r="B40" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="73" t="s">
+      <c r="C40" s="125" t="s">
         <v>54</v>
       </c>
-      <c r="D40" s="74"/>
-      <c r="E40" s="74"/>
-      <c r="F40" s="75"/>
+      <c r="D40" s="126"/>
+      <c r="E40" s="126"/>
+      <c r="F40" s="127"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B42" s="2" t="s">
@@ -2671,25 +2671,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C39:F39"/>
@@ -2704,6 +2685,25 @@
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C24:F24"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2831,12 +2831,12 @@
       <c r="A8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="100" t="s">
+      <c r="C8" s="97" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
@@ -2859,48 +2859,48 @@
       <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="191" t="s">
+      <c r="C10" s="153" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="192"/>
-      <c r="E10" s="192"/>
-      <c r="F10" s="193"/>
+      <c r="D10" s="154"/>
+      <c r="E10" s="154"/>
+      <c r="F10" s="155"/>
     </row>
     <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="25"/>
       <c r="B11" s="26">
         <v>2</v>
       </c>
-      <c r="C11" s="194" t="s">
+      <c r="C11" s="156" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="195"/>
-      <c r="E11" s="195"/>
-      <c r="F11" s="196"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="157"/>
+      <c r="F11" s="158"/>
     </row>
     <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
       <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="167" t="s">
+      <c r="C12" s="162" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="203"/>
-      <c r="E12" s="204" t="s">
+      <c r="D12" s="168"/>
+      <c r="E12" s="169" t="s">
         <v>87</v>
       </c>
-      <c r="F12" s="169"/>
+      <c r="F12" s="164"/>
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="27"/>
       <c r="B13" s="28">
         <v>4</v>
       </c>
-      <c r="C13" s="197"/>
-      <c r="D13" s="198"/>
-      <c r="E13" s="198"/>
-      <c r="F13" s="199"/>
+      <c r="C13" s="159"/>
+      <c r="D13" s="160"/>
+      <c r="E13" s="160"/>
+      <c r="F13" s="161"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="29" t="s">
@@ -2909,56 +2909,56 @@
       <c r="B14" s="30">
         <v>1</v>
       </c>
-      <c r="C14" s="200" t="s">
+      <c r="C14" s="165" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="201"/>
-      <c r="E14" s="201"/>
-      <c r="F14" s="202"/>
+      <c r="D14" s="166"/>
+      <c r="E14" s="166"/>
+      <c r="F14" s="167"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="25"/>
       <c r="B15" s="26">
         <v>2</v>
       </c>
-      <c r="C15" s="167" t="s">
+      <c r="C15" s="162" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="168"/>
-      <c r="E15" s="168"/>
-      <c r="F15" s="169"/>
+      <c r="D15" s="163"/>
+      <c r="E15" s="163"/>
+      <c r="F15" s="164"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
       <c r="B16" s="26">
         <v>3</v>
       </c>
-      <c r="C16" s="91"/>
-      <c r="D16" s="92"/>
-      <c r="E16" s="92"/>
-      <c r="F16" s="93"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="139"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="140"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="25"/>
       <c r="B17" s="26">
         <v>4</v>
       </c>
-      <c r="C17" s="167" t="s">
+      <c r="C17" s="162" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="168"/>
-      <c r="E17" s="168"/>
-      <c r="F17" s="169"/>
+      <c r="D17" s="163"/>
+      <c r="E17" s="163"/>
+      <c r="F17" s="164"/>
     </row>
     <row r="18" spans="1:9" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="31"/>
       <c r="B18" s="28">
         <v>5</v>
       </c>
-      <c r="C18" s="188"/>
-      <c r="D18" s="189"/>
-      <c r="E18" s="189"/>
-      <c r="F18" s="190"/>
+      <c r="C18" s="150"/>
+      <c r="D18" s="151"/>
+      <c r="E18" s="151"/>
+      <c r="F18" s="152"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" s="29" t="s">
@@ -2967,52 +2967,52 @@
       <c r="B19" s="30">
         <v>1</v>
       </c>
-      <c r="C19" s="176"/>
-      <c r="D19" s="177"/>
-      <c r="E19" s="177"/>
-      <c r="F19" s="178"/>
+      <c r="C19" s="173"/>
+      <c r="D19" s="174"/>
+      <c r="E19" s="174"/>
+      <c r="F19" s="175"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="25"/>
       <c r="B20" s="26">
         <v>2</v>
       </c>
-      <c r="C20" s="179" t="s">
+      <c r="C20" s="176" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="180"/>
-      <c r="E20" s="180"/>
-      <c r="F20" s="181"/>
+      <c r="D20" s="177"/>
+      <c r="E20" s="177"/>
+      <c r="F20" s="178"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" s="25"/>
       <c r="B21" s="26">
         <v>3</v>
       </c>
-      <c r="C21" s="182"/>
-      <c r="D21" s="183"/>
-      <c r="E21" s="183"/>
-      <c r="F21" s="184"/>
+      <c r="C21" s="179"/>
+      <c r="D21" s="180"/>
+      <c r="E21" s="180"/>
+      <c r="F21" s="181"/>
     </row>
     <row r="22" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="25"/>
       <c r="B22" s="26">
         <v>4</v>
       </c>
-      <c r="C22" s="182"/>
-      <c r="D22" s="183"/>
-      <c r="E22" s="183"/>
-      <c r="F22" s="184"/>
+      <c r="C22" s="179"/>
+      <c r="D22" s="180"/>
+      <c r="E22" s="180"/>
+      <c r="F22" s="181"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="31"/>
       <c r="B23" s="28">
         <v>5</v>
       </c>
-      <c r="C23" s="144"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="145"/>
-      <c r="F23" s="146"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="90"/>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="29" t="s">
@@ -3021,22 +3021,22 @@
       <c r="B24" s="30">
         <v>3</v>
       </c>
-      <c r="C24" s="185"/>
-      <c r="D24" s="186"/>
-      <c r="E24" s="186"/>
-      <c r="F24" s="187"/>
+      <c r="C24" s="182"/>
+      <c r="D24" s="183"/>
+      <c r="E24" s="183"/>
+      <c r="F24" s="184"/>
     </row>
     <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="25"/>
       <c r="B25" s="26">
         <v>4</v>
       </c>
-      <c r="C25" s="79" t="s">
+      <c r="C25" s="94" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="81"/>
+      <c r="D25" s="95"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="96"/>
       <c r="I25" s="53"/>
     </row>
     <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -3044,32 +3044,32 @@
       <c r="B26" s="26">
         <v>5</v>
       </c>
-      <c r="C26" s="91"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="93"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="140"/>
     </row>
     <row r="27" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="32"/>
       <c r="B27" s="33">
         <v>6</v>
       </c>
-      <c r="C27" s="167" t="s">
+      <c r="C27" s="162" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="168"/>
-      <c r="E27" s="168"/>
-      <c r="F27" s="169"/>
+      <c r="D27" s="163"/>
+      <c r="E27" s="163"/>
+      <c r="F27" s="164"/>
     </row>
     <row r="28" spans="1:9" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="31"/>
       <c r="B28" s="28">
         <v>7</v>
       </c>
-      <c r="C28" s="173"/>
-      <c r="D28" s="174"/>
-      <c r="E28" s="174"/>
-      <c r="F28" s="175"/>
+      <c r="C28" s="170"/>
+      <c r="D28" s="171"/>
+      <c r="E28" s="171"/>
+      <c r="F28" s="172"/>
       <c r="I28" s="53"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.4">
@@ -3079,44 +3079,44 @@
       <c r="B29" s="30">
         <v>3</v>
       </c>
-      <c r="C29" s="101" t="s">
+      <c r="C29" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="153"/>
-      <c r="E29" s="153"/>
-      <c r="F29" s="154"/>
+      <c r="D29" s="188"/>
+      <c r="E29" s="188"/>
+      <c r="F29" s="189"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A30" s="34"/>
       <c r="B30" s="26">
         <v>4</v>
       </c>
-      <c r="C30" s="167" t="s">
+      <c r="C30" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="168"/>
-      <c r="E30" s="168"/>
-      <c r="F30" s="169"/>
+      <c r="D30" s="163"/>
+      <c r="E30" s="163"/>
+      <c r="F30" s="164"/>
     </row>
     <row r="31" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="34"/>
       <c r="B31" s="26">
         <v>5</v>
       </c>
-      <c r="C31" s="170"/>
-      <c r="D31" s="171"/>
-      <c r="E31" s="171"/>
-      <c r="F31" s="172"/>
+      <c r="C31" s="202"/>
+      <c r="D31" s="203"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="204"/>
     </row>
     <row r="32" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="54"/>
       <c r="B32" s="28">
         <v>6</v>
       </c>
-      <c r="C32" s="155"/>
-      <c r="D32" s="156"/>
-      <c r="E32" s="156"/>
-      <c r="F32" s="157"/>
+      <c r="C32" s="190"/>
+      <c r="D32" s="191"/>
+      <c r="E32" s="191"/>
+      <c r="F32" s="192"/>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="71" t="s">
@@ -3125,86 +3125,86 @@
       <c r="B33" s="60">
         <v>1</v>
       </c>
-      <c r="C33" s="158"/>
-      <c r="D33" s="159"/>
-      <c r="E33" s="159"/>
-      <c r="F33" s="160"/>
+      <c r="C33" s="193"/>
+      <c r="D33" s="194"/>
+      <c r="E33" s="194"/>
+      <c r="F33" s="195"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="61"/>
       <c r="B34" s="68">
         <v>2</v>
       </c>
-      <c r="C34" s="164"/>
-      <c r="D34" s="165"/>
-      <c r="E34" s="165"/>
-      <c r="F34" s="166"/>
+      <c r="C34" s="199"/>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="201"/>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="61"/>
       <c r="B35" s="68">
         <v>3</v>
       </c>
-      <c r="C35" s="164"/>
-      <c r="D35" s="165"/>
-      <c r="E35" s="165"/>
-      <c r="F35" s="166"/>
+      <c r="C35" s="199"/>
+      <c r="D35" s="200"/>
+      <c r="E35" s="200"/>
+      <c r="F35" s="201"/>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="72"/>
       <c r="B36" s="69">
         <v>4</v>
       </c>
-      <c r="C36" s="73" t="s">
+      <c r="C36" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="D36" s="74"/>
-      <c r="E36" s="74"/>
-      <c r="F36" s="75"/>
+      <c r="D36" s="126"/>
+      <c r="E36" s="126"/>
+      <c r="F36" s="127"/>
     </row>
     <row r="37" spans="1:6" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="70"/>
       <c r="B37" s="42"/>
-      <c r="C37" s="161"/>
-      <c r="D37" s="162"/>
-      <c r="E37" s="162"/>
-      <c r="F37" s="163"/>
+      <c r="C37" s="196"/>
+      <c r="D37" s="197"/>
+      <c r="E37" s="197"/>
+      <c r="F37" s="198"/>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="62"/>
       <c r="B38" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="C38" s="76" t="s">
+      <c r="C38" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="D38" s="77"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="78"/>
+      <c r="D38" s="129"/>
+      <c r="E38" s="129"/>
+      <c r="F38" s="130"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="63"/>
       <c r="B39" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="167" t="s">
+      <c r="C39" s="162" t="s">
         <v>58</v>
       </c>
-      <c r="D39" s="168"/>
-      <c r="E39" s="168"/>
-      <c r="F39" s="169"/>
+      <c r="D39" s="163"/>
+      <c r="E39" s="163"/>
+      <c r="F39" s="164"/>
     </row>
     <row r="40" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A40" s="64"/>
       <c r="B40" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="150" t="s">
+      <c r="C40" s="185" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="151"/>
-      <c r="E40" s="151"/>
-      <c r="F40" s="152"/>
+      <c r="D40" s="186"/>
+      <c r="E40" s="186"/>
+      <c r="F40" s="187"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B42" s="2" t="s">
@@ -3224,27 +3224,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C23:F23"/>
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C32:F32"/>
@@ -3257,6 +3236,27 @@
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3383,12 +3383,12 @@
       <c r="A8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="100" t="s">
+      <c r="C8" s="97" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
     </row>
     <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
@@ -3411,44 +3411,44 @@
       <c r="B10" s="30">
         <v>1</v>
       </c>
-      <c r="C10" s="241" t="s">
+      <c r="C10" s="226" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="242"/>
-      <c r="E10" s="242"/>
-      <c r="F10" s="243"/>
+      <c r="D10" s="227"/>
+      <c r="E10" s="227"/>
+      <c r="F10" s="228"/>
     </row>
     <row r="11" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="25"/>
       <c r="B11" s="26">
         <v>2</v>
       </c>
-      <c r="C11" s="208" t="s">
+      <c r="C11" s="205" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="209"/>
-      <c r="E11" s="209"/>
-      <c r="F11" s="210"/>
+      <c r="D11" s="206"/>
+      <c r="E11" s="206"/>
+      <c r="F11" s="207"/>
     </row>
     <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
       <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="138"/>
-      <c r="D12" s="139"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="140"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="84"/>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="27"/>
       <c r="B13" s="28">
         <v>4</v>
       </c>
-      <c r="C13" s="223"/>
-      <c r="D13" s="224"/>
-      <c r="E13" s="224"/>
-      <c r="F13" s="225"/>
+      <c r="C13" s="208"/>
+      <c r="D13" s="209"/>
+      <c r="E13" s="209"/>
+      <c r="F13" s="210"/>
     </row>
     <row r="14" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="29" t="s">
@@ -3457,46 +3457,46 @@
       <c r="B14" s="30">
         <v>1</v>
       </c>
-      <c r="C14" s="244" t="s">
+      <c r="C14" s="229" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="245"/>
-      <c r="E14" s="245"/>
-      <c r="F14" s="246"/>
+      <c r="D14" s="230"/>
+      <c r="E14" s="230"/>
+      <c r="F14" s="231"/>
     </row>
     <row r="15" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="25"/>
       <c r="B15" s="26">
         <v>2</v>
       </c>
-      <c r="C15" s="235" t="s">
+      <c r="C15" s="220" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="236"/>
-      <c r="E15" s="236"/>
-      <c r="F15" s="237"/>
+      <c r="D15" s="221"/>
+      <c r="E15" s="221"/>
+      <c r="F15" s="222"/>
     </row>
     <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
       <c r="B16" s="26">
         <v>3</v>
       </c>
-      <c r="C16" s="238" t="s">
+      <c r="C16" s="223" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="239"/>
-      <c r="E16" s="239"/>
-      <c r="F16" s="240"/>
+      <c r="D16" s="224"/>
+      <c r="E16" s="224"/>
+      <c r="F16" s="225"/>
     </row>
     <row r="17" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="31"/>
       <c r="B17" s="28">
         <v>4</v>
       </c>
-      <c r="C17" s="229"/>
-      <c r="D17" s="230"/>
-      <c r="E17" s="230"/>
-      <c r="F17" s="231"/>
+      <c r="C17" s="214"/>
+      <c r="D17" s="215"/>
+      <c r="E17" s="215"/>
+      <c r="F17" s="216"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="29" t="s">
@@ -3505,44 +3505,44 @@
       <c r="B18" s="30">
         <v>1</v>
       </c>
-      <c r="C18" s="158"/>
-      <c r="D18" s="159"/>
-      <c r="E18" s="159"/>
-      <c r="F18" s="160"/>
+      <c r="C18" s="193"/>
+      <c r="D18" s="194"/>
+      <c r="E18" s="194"/>
+      <c r="F18" s="195"/>
     </row>
     <row r="19" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="25"/>
       <c r="B19" s="26">
         <v>2</v>
       </c>
-      <c r="C19" s="232" t="s">
+      <c r="C19" s="217" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="233"/>
-      <c r="E19" s="233"/>
-      <c r="F19" s="234"/>
+      <c r="D19" s="218"/>
+      <c r="E19" s="218"/>
+      <c r="F19" s="219"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="25"/>
       <c r="B20" s="26">
         <v>3</v>
       </c>
-      <c r="C20" s="226" t="s">
+      <c r="C20" s="211" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="227"/>
-      <c r="E20" s="227"/>
-      <c r="F20" s="228"/>
+      <c r="D20" s="212"/>
+      <c r="E20" s="212"/>
+      <c r="F20" s="213"/>
     </row>
     <row r="21" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="31"/>
       <c r="B21" s="28">
         <v>4</v>
       </c>
-      <c r="C21" s="123"/>
-      <c r="D21" s="124"/>
-      <c r="E21" s="124"/>
-      <c r="F21" s="125"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="124"/>
     </row>
     <row r="22" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="29" t="s">
@@ -3551,44 +3551,44 @@
       <c r="B22" s="30">
         <v>1</v>
       </c>
-      <c r="C22" s="247"/>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248"/>
-      <c r="F22" s="249"/>
+      <c r="C22" s="232"/>
+      <c r="D22" s="233"/>
+      <c r="E22" s="233"/>
+      <c r="F22" s="234"/>
     </row>
     <row r="23" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="25"/>
       <c r="B23" s="26">
         <v>2</v>
       </c>
-      <c r="C23" s="232" t="s">
+      <c r="C23" s="217" t="s">
         <v>92</v>
       </c>
-      <c r="D23" s="233"/>
-      <c r="E23" s="233"/>
-      <c r="F23" s="234"/>
+      <c r="D23" s="218"/>
+      <c r="E23" s="218"/>
+      <c r="F23" s="219"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="25"/>
       <c r="B24" s="26">
         <v>3</v>
       </c>
-      <c r="C24" s="226" t="s">
+      <c r="C24" s="211" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="227"/>
-      <c r="E24" s="227"/>
-      <c r="F24" s="228"/>
+      <c r="D24" s="212"/>
+      <c r="E24" s="212"/>
+      <c r="F24" s="213"/>
     </row>
     <row r="25" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="31"/>
       <c r="B25" s="28">
         <v>4</v>
       </c>
-      <c r="C25" s="205"/>
-      <c r="D25" s="206"/>
-      <c r="E25" s="206"/>
-      <c r="F25" s="207"/>
+      <c r="C25" s="235"/>
+      <c r="D25" s="236"/>
+      <c r="E25" s="236"/>
+      <c r="F25" s="237"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="29" t="s">
@@ -3597,48 +3597,48 @@
       <c r="B26" s="30">
         <v>1</v>
       </c>
-      <c r="C26" s="220" t="s">
+      <c r="C26" s="247" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="221"/>
-      <c r="E26" s="221"/>
-      <c r="F26" s="222"/>
+      <c r="D26" s="248"/>
+      <c r="E26" s="248"/>
+      <c r="F26" s="249"/>
     </row>
     <row r="27" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="34"/>
       <c r="B27" s="26">
         <v>2</v>
       </c>
-      <c r="C27" s="217" t="s">
+      <c r="C27" s="244" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="218"/>
-      <c r="E27" s="218"/>
-      <c r="F27" s="219"/>
+      <c r="D27" s="245"/>
+      <c r="E27" s="245"/>
+      <c r="F27" s="246"/>
     </row>
     <row r="28" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="34"/>
       <c r="B28" s="26">
         <v>3</v>
       </c>
-      <c r="C28" s="208" t="s">
+      <c r="C28" s="205" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="209"/>
-      <c r="E28" s="209"/>
-      <c r="F28" s="210"/>
+      <c r="D28" s="206"/>
+      <c r="E28" s="206"/>
+      <c r="F28" s="207"/>
     </row>
     <row r="29" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="54"/>
       <c r="B29" s="28">
         <v>4</v>
       </c>
-      <c r="C29" s="211" t="s">
+      <c r="C29" s="238" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="212"/>
-      <c r="E29" s="212"/>
-      <c r="F29" s="213"/>
+      <c r="D29" s="239"/>
+      <c r="E29" s="239"/>
+      <c r="F29" s="240"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="37" t="s">
@@ -3647,44 +3647,44 @@
       <c r="B30" s="30">
         <v>1</v>
       </c>
-      <c r="C30" s="214"/>
-      <c r="D30" s="215"/>
-      <c r="E30" s="215"/>
-      <c r="F30" s="216"/>
+      <c r="C30" s="241"/>
+      <c r="D30" s="242"/>
+      <c r="E30" s="242"/>
+      <c r="F30" s="243"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="38"/>
       <c r="B31" s="26">
         <v>2</v>
       </c>
-      <c r="C31" s="129"/>
-      <c r="D31" s="130"/>
-      <c r="E31" s="130"/>
-      <c r="F31" s="131"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="75"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="38"/>
       <c r="B32" s="26">
         <v>3</v>
       </c>
-      <c r="C32" s="179" t="s">
+      <c r="C32" s="176" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="180"/>
-      <c r="E32" s="180"/>
-      <c r="F32" s="181"/>
+      <c r="D32" s="177"/>
+      <c r="E32" s="177"/>
+      <c r="F32" s="178"/>
     </row>
     <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="40"/>
       <c r="B33" s="28">
         <v>4</v>
       </c>
-      <c r="C33" s="126" t="s">
+      <c r="C33" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="127"/>
-      <c r="E33" s="127"/>
-      <c r="F33" s="128"/>
+      <c r="D33" s="148"/>
+      <c r="E33" s="148"/>
+      <c r="F33" s="149"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B35" s="2" t="s">
@@ -3704,6 +3704,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C32:F32"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C13:F13"/>
@@ -3720,15 +3729,6 @@
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C32:F32"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3866,10 +3866,10 @@
       <c r="A9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="100" t="s">
+      <c r="C9" s="97" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="100"/>
+      <c r="D9" s="97"/>
       <c r="E9" s="57"/>
     </row>
     <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3893,56 +3893,56 @@
       <c r="B11" s="24">
         <v>2</v>
       </c>
-      <c r="C11" s="253"/>
-      <c r="D11" s="254"/>
-      <c r="E11" s="254"/>
-      <c r="F11" s="255"/>
+      <c r="C11" s="265"/>
+      <c r="D11" s="266"/>
+      <c r="E11" s="266"/>
+      <c r="F11" s="267"/>
     </row>
     <row r="12" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
       <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="217" t="s">
+      <c r="C12" s="244" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="218"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="140"/>
+      <c r="D12" s="245"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="84"/>
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="25"/>
       <c r="B13" s="26">
         <v>4</v>
       </c>
-      <c r="C13" s="217" t="s">
+      <c r="C13" s="244" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="218"/>
-      <c r="E13" s="218"/>
-      <c r="F13" s="219"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="245"/>
+      <c r="F13" s="246"/>
     </row>
     <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="25"/>
       <c r="B14" s="26">
         <v>5</v>
       </c>
-      <c r="C14" s="256" t="s">
+      <c r="C14" s="268" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="257"/>
-      <c r="E14" s="257"/>
-      <c r="F14" s="258"/>
+      <c r="D14" s="269"/>
+      <c r="E14" s="269"/>
+      <c r="F14" s="270"/>
     </row>
     <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="27"/>
       <c r="B15" s="28">
         <v>6</v>
       </c>
-      <c r="C15" s="111"/>
-      <c r="D15" s="112"/>
-      <c r="E15" s="112"/>
-      <c r="F15" s="113"/>
+      <c r="C15" s="110"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="112"/>
     </row>
     <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="29" t="s">
@@ -3951,46 +3951,46 @@
       <c r="B16" s="30">
         <v>1</v>
       </c>
-      <c r="C16" s="114" t="s">
+      <c r="C16" s="113" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="116"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="115"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="25"/>
       <c r="B17" s="26">
         <v>2</v>
       </c>
-      <c r="C17" s="250" t="s">
+      <c r="C17" s="264" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="251"/>
-      <c r="E17" s="251"/>
-      <c r="F17" s="252"/>
+      <c r="D17" s="250"/>
+      <c r="E17" s="250"/>
+      <c r="F17" s="251"/>
     </row>
     <row r="18" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="25"/>
       <c r="B18" s="26">
         <v>3</v>
       </c>
-      <c r="C18" s="262"/>
-      <c r="D18" s="263"/>
-      <c r="E18" s="251" t="s">
+      <c r="C18" s="271"/>
+      <c r="D18" s="272"/>
+      <c r="E18" s="250" t="s">
         <v>99</v>
       </c>
-      <c r="F18" s="252"/>
+      <c r="F18" s="251"/>
     </row>
     <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="31"/>
       <c r="B19" s="28">
         <v>4</v>
       </c>
-      <c r="C19" s="229"/>
-      <c r="D19" s="230"/>
-      <c r="E19" s="230"/>
-      <c r="F19" s="231"/>
+      <c r="C19" s="214"/>
+      <c r="D19" s="215"/>
+      <c r="E19" s="215"/>
+      <c r="F19" s="216"/>
     </row>
     <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="29" t="s">
@@ -3999,46 +3999,46 @@
       <c r="B20" s="30">
         <v>1</v>
       </c>
-      <c r="C20" s="135" t="s">
+      <c r="C20" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="136"/>
-      <c r="E20" s="136"/>
-      <c r="F20" s="137"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="81"/>
     </row>
     <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="25"/>
       <c r="B21" s="26">
         <v>2</v>
       </c>
-      <c r="C21" s="85" t="s">
+      <c r="C21" s="134" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
-      <c r="F21" s="87"/>
+      <c r="D21" s="135"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="136"/>
     </row>
     <row r="22" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="25"/>
       <c r="B22" s="26">
         <v>3</v>
       </c>
-      <c r="C22" s="167" t="s">
+      <c r="C22" s="162" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="168"/>
-      <c r="E22" s="168"/>
-      <c r="F22" s="169"/>
+      <c r="D22" s="163"/>
+      <c r="E22" s="163"/>
+      <c r="F22" s="164"/>
     </row>
     <row r="23" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="31"/>
       <c r="B23" s="28">
         <v>4</v>
       </c>
-      <c r="C23" s="223"/>
-      <c r="D23" s="224"/>
-      <c r="E23" s="224"/>
-      <c r="F23" s="225"/>
+      <c r="C23" s="208"/>
+      <c r="D23" s="209"/>
+      <c r="E23" s="209"/>
+      <c r="F23" s="210"/>
     </row>
     <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="29" t="s">
@@ -4047,42 +4047,42 @@
       <c r="B24" s="30">
         <v>1</v>
       </c>
-      <c r="C24" s="259" t="s">
+      <c r="C24" s="255" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="260"/>
-      <c r="E24" s="260"/>
-      <c r="F24" s="261"/>
+      <c r="D24" s="256"/>
+      <c r="E24" s="256"/>
+      <c r="F24" s="257"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="25"/>
       <c r="B25" s="26">
         <v>2</v>
       </c>
-      <c r="C25" s="91"/>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92"/>
-      <c r="F25" s="93"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="140"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="25"/>
       <c r="B26" s="26">
         <v>3</v>
       </c>
-      <c r="C26" s="91"/>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="93"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="140"/>
     </row>
     <row r="27" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="31"/>
       <c r="B27" s="28">
         <v>4</v>
       </c>
-      <c r="C27" s="123"/>
-      <c r="D27" s="124"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="125"/>
+      <c r="C27" s="122"/>
+      <c r="D27" s="123"/>
+      <c r="E27" s="123"/>
+      <c r="F27" s="124"/>
     </row>
     <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="29" t="s">
@@ -4091,46 +4091,46 @@
       <c r="B28" s="30">
         <v>2</v>
       </c>
-      <c r="C28" s="267"/>
-      <c r="D28" s="268"/>
-      <c r="E28" s="268"/>
-      <c r="F28" s="269"/>
+      <c r="C28" s="258"/>
+      <c r="D28" s="259"/>
+      <c r="E28" s="259"/>
+      <c r="F28" s="260"/>
     </row>
     <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="34"/>
       <c r="B29" s="26">
         <v>3</v>
       </c>
-      <c r="C29" s="167" t="s">
+      <c r="C29" s="162" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="168"/>
-      <c r="E29" s="168"/>
-      <c r="F29" s="169"/>
+      <c r="D29" s="163"/>
+      <c r="E29" s="163"/>
+      <c r="F29" s="164"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="34"/>
       <c r="B30" s="26">
         <v>4</v>
       </c>
-      <c r="C30" s="264" t="s">
+      <c r="C30" s="252" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="265"/>
-      <c r="E30" s="265"/>
-      <c r="F30" s="266"/>
+      <c r="D30" s="253"/>
+      <c r="E30" s="253"/>
+      <c r="F30" s="254"/>
     </row>
     <row r="31" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="54"/>
       <c r="B31" s="28">
         <v>5</v>
       </c>
-      <c r="C31" s="270" t="s">
+      <c r="C31" s="261" t="s">
         <v>51</v>
       </c>
-      <c r="D31" s="271"/>
-      <c r="E31" s="271"/>
-      <c r="F31" s="272"/>
+      <c r="D31" s="262"/>
+      <c r="E31" s="262"/>
+      <c r="F31" s="263"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="56" t="s">
@@ -4139,40 +4139,40 @@
       <c r="B32" s="24">
         <v>1</v>
       </c>
-      <c r="C32" s="259" t="s">
+      <c r="C32" s="255" t="s">
         <v>98</v>
       </c>
-      <c r="D32" s="260"/>
-      <c r="E32" s="260"/>
-      <c r="F32" s="261"/>
+      <c r="D32" s="256"/>
+      <c r="E32" s="256"/>
+      <c r="F32" s="257"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="38"/>
       <c r="B33" s="26">
         <v>2</v>
       </c>
-      <c r="C33" s="91"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="93"/>
+      <c r="C33" s="138"/>
+      <c r="D33" s="139"/>
+      <c r="E33" s="139"/>
+      <c r="F33" s="140"/>
     </row>
     <row r="34" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="38"/>
       <c r="B34" s="26">
         <v>3</v>
       </c>
-      <c r="C34" s="91"/>
-      <c r="D34" s="92"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93"/>
+      <c r="C34" s="138"/>
+      <c r="D34" s="139"/>
+      <c r="E34" s="139"/>
+      <c r="F34" s="140"/>
     </row>
     <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="46"/>
       <c r="B35" s="55"/>
-      <c r="C35" s="144"/>
-      <c r="D35" s="145"/>
-      <c r="E35" s="145"/>
-      <c r="F35" s="146"/>
+      <c r="C35" s="88"/>
+      <c r="D35" s="89"/>
+      <c r="E35" s="89"/>
+      <c r="F35" s="90"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B37" s="2" t="s">
@@ -4192,18 +4192,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C31:F31"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="C22:F22"/>
@@ -4220,6 +4208,18 @@
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C31:F31"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">

--- a/input/timetable/Физическая культура_.xlsx
+++ b/input/timetable/Физическая культура_.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13890" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13890"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="145">
   <si>
     <t>пара</t>
   </si>
@@ -74,6 +74,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -128,33 +131,78 @@
     <t>Лыжный спорт с методикой преподавания, л/б</t>
   </si>
   <si>
+    <t>Снигирев А.С., Ветошников А.Ю.</t>
+  </si>
+  <si>
+    <t>Аустер Л.В., Родионова М.А.</t>
+  </si>
+  <si>
     <t>Гимнастика с методикой преподавания, Зал гимн.</t>
   </si>
   <si>
+    <t>Булгакова О.В., Савиных Л.Е.</t>
+  </si>
+  <si>
     <t>Спортивно-педагогические дисциплины, Зал гимн</t>
   </si>
   <si>
+    <t>Савиных Л.Е., Булгакова О.В.</t>
+  </si>
+  <si>
+    <t>Обухов С.М.</t>
+  </si>
+  <si>
+    <t>Шнейдер В.Ю.</t>
+  </si>
+  <si>
     <t>Теория и методика физической культуры (пр), К425</t>
   </si>
   <si>
     <t>Работа в команде (лек 32 ч)</t>
   </si>
   <si>
+    <t>Снигирев А.С., Обухов С.М.</t>
+  </si>
+  <si>
+    <t>Лосев А.В.</t>
+  </si>
+  <si>
+    <t>Родионов В.А.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Алькова С.Ю.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (пр), К209</t>
   </si>
   <si>
+    <t>Ветошников А.Ю.</t>
+  </si>
+  <si>
+    <t>Родионова М.А.</t>
+  </si>
+  <si>
+    <t>Савиных Л.Е.</t>
+  </si>
+  <si>
     <t>Теория спорта (лек), ЭОиДОТ</t>
   </si>
   <si>
     <t>Теория спорта (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Григорьев В.А.</t>
+  </si>
+  <si>
     <t>Менеджмент физической культуры и спорта (лек), К425</t>
   </si>
   <si>
+    <t>Куяров А.В.</t>
+  </si>
+  <si>
     <t>Внетренировочные факторы повышения результативности (лек). К209</t>
   </si>
   <si>
@@ -164,6 +212,9 @@
     <t>205-31</t>
   </si>
   <si>
+    <t>Белоус П.В.</t>
+  </si>
+  <si>
     <t>Плавание с методикой преподавания/Спортивно-педагогические дисциплины, Бассейн (с 11.45)</t>
   </si>
   <si>
@@ -173,6 +224,9 @@
     <t xml:space="preserve">ДВ 02.01: Футбол, зал 2; ДВ 02.02: Аэробика, сп/з </t>
   </si>
   <si>
+    <t>Ветошников А.Ю.; Булгакова О.В.</t>
+  </si>
+  <si>
     <t>Спортивная социология (лек), К209</t>
   </si>
   <si>
@@ -191,6 +245,15 @@
     <t>История России (лекция 32 ч)</t>
   </si>
   <si>
+    <t>Галлямова Л.В.</t>
+  </si>
+  <si>
+    <t>Обухов С.М., Снигирев А.С.</t>
+  </si>
+  <si>
+    <t>Говорухина А.А.</t>
+  </si>
+  <si>
     <t>Легкая атлетика с методикой преподавания, ЦАС</t>
   </si>
   <si>
@@ -209,12 +272,18 @@
     <t>Легкая атлетика с методикой преподавания,  ЦАС</t>
   </si>
   <si>
+    <t>Лосев В.Ю.</t>
+  </si>
+  <si>
     <t>Нормативно-правовые основы профессиональной деятельности (лек)/(пр), К425 (с 17.00)</t>
   </si>
   <si>
     <t>Теория и методика физической культуры (лек), К425</t>
   </si>
   <si>
+    <t>Кочиева Д.И.</t>
+  </si>
+  <si>
     <t>Формирование культуры здорового образа жизни (пр), К210а</t>
   </si>
   <si>
@@ -254,15 +323,51 @@
     <t>02.02.2026-08.04.2026</t>
   </si>
   <si>
+    <t>Вариясова Е.В.</t>
+  </si>
+  <si>
+    <t>Воробьева А.Д. ; Джумаева А.А.</t>
+  </si>
+  <si>
     <t>//Спортивно-педагогические дисциплины, ЦАС</t>
   </si>
   <si>
+    <t>Литовченко О.Г.</t>
+  </si>
+  <si>
     <t>Биохимия мышечной деятельности (лек)/(пр), А539/А439</t>
   </si>
   <si>
+    <t>Лосев А.В., Ветрова Д.Н.</t>
+  </si>
+  <si>
+    <t>Гаврилова Н.В.</t>
+  </si>
+  <si>
+    <t>Савш И.Ю.; Джумаева А.А.</t>
+  </si>
+  <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
+    <t>Осипова А.В.</t>
+  </si>
+  <si>
+    <t>Ветрова Д.Н.</t>
+  </si>
+  <si>
     <t>Спортивно-педагогические дисциплины,  ЦАС</t>
   </si>
   <si>
+    <t>Мальков М.Н.</t>
+  </si>
+  <si>
+    <t>Воронюк Т.В.</t>
+  </si>
+  <si>
+    <t>Булгакова О.В.</t>
+  </si>
+  <si>
     <t>Хоккей, зал 2</t>
   </si>
   <si>
@@ -281,9 +386,18 @@
     <t>Иностранный язык, п/г 2, К517</t>
   </si>
   <si>
+    <t>Алькова С.Ю</t>
+  </si>
+  <si>
+    <t>.Ветрова Д.Н.</t>
+  </si>
+  <si>
     <t>Учебная практика, ознакомительная практика, К425</t>
   </si>
   <si>
+    <t>Осипова А.В./Калинина Е.А.</t>
+  </si>
+  <si>
     <t>Работа в команде (пр), К427// Философия (пр), К427</t>
   </si>
   <si>
@@ -339,6 +453,9 @@
   </si>
   <si>
     <t xml:space="preserve">Психология физической культуры (лек), К202// </t>
+  </si>
+  <si>
+    <t>Барсегян С.Г.</t>
   </si>
   <si>
     <t>Физиология человека (пр), А431//</t>
@@ -442,7 +559,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -461,12 +578,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -583,6 +706,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -712,6 +848,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1051,6 +1200,17 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1199,7 +1359,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="273">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1239,28 +1399,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1284,98 +1447,251 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1384,16 +1700,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1402,434 +1718,280 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1838,11 +2000,41 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
@@ -2172,7 +2364,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T43"/>
+  <dimension ref="A1:U43"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2181,12 +2373,13 @@
     <col min="4" max="4" width="18.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="20" style="2" customWidth="1"/>
-    <col min="7" max="13" width="9.140625" style="2"/>
-    <col min="14" max="14" width="9" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="25.140625" style="2" customWidth="1"/>
+    <col min="8" max="14" width="9.140625" style="2"/>
+    <col min="15" max="15" width="9" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2194,15 +2387,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2210,41 +2403,41 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="47" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="47"/>
+      <c r="C6" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="51"/>
       <c r="E6" s="10">
         <v>1</v>
       </c>
@@ -2252,35 +2445,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="48"/>
+      <c r="D7" s="52"/>
       <c r="E7" s="15" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="97" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="97"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="128" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="128"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>0</v>
@@ -2291,369 +2484,445 @@
       <c r="D9" s="20"/>
       <c r="E9" s="21"/>
       <c r="F9" s="22"/>
-    </row>
-    <row r="10" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="24">
+      <c r="G9" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="25">
         <v>1</v>
       </c>
-      <c r="C10" s="104" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" s="105"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="106"/>
-    </row>
-    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="C10" s="133" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="134"/>
+      <c r="E10" s="134"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="90" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <v>2</v>
       </c>
-      <c r="C11" s="107" t="s">
+      <c r="C11" s="136" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="138"/>
+      <c r="G11" s="87" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
+        <v>3</v>
+      </c>
+      <c r="C12" s="130" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="87" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
+        <v>4</v>
+      </c>
+      <c r="C13" s="130" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="88" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29">
+        <v>5</v>
+      </c>
+      <c r="C14" s="139"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="141"/>
+      <c r="G14" s="81"/>
+    </row>
+    <row r="15" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="31">
+        <v>1</v>
+      </c>
+      <c r="C15" s="142" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" s="143"/>
+      <c r="E15" s="143"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="90" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>2</v>
+      </c>
+      <c r="C16" s="145"/>
+      <c r="D16" s="146"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="147"/>
+      <c r="G16" s="82"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
+        <v>3</v>
+      </c>
+      <c r="C17" s="148" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="149"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="150"/>
+      <c r="G17" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="108"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="109"/>
-    </row>
-    <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+    </row>
+    <row r="18" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="32"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="151"/>
+      <c r="D18" s="152"/>
+      <c r="E18" s="152"/>
+      <c r="F18" s="153"/>
+      <c r="G18" s="82"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A19" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="31">
+        <v>1</v>
+      </c>
+      <c r="C19" s="129" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="117"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="118"/>
+      <c r="G19" s="90" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
+        <v>2</v>
+      </c>
+      <c r="C20" s="157"/>
+      <c r="D20" s="158"/>
+      <c r="E20" s="158"/>
+      <c r="F20" s="159"/>
+      <c r="G20" s="82"/>
+    </row>
+    <row r="21" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="101" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="102"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="103"/>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="C21" s="160" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="161"/>
+      <c r="E21" s="161"/>
+      <c r="F21" s="162"/>
+      <c r="G21" s="92" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="32"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="172"/>
+      <c r="D22" s="173"/>
+      <c r="E22" s="173"/>
+      <c r="F22" s="174"/>
+      <c r="G22" s="81"/>
+    </row>
+    <row r="23" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="31">
+        <v>1</v>
+      </c>
+      <c r="C23" s="163" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="164"/>
+      <c r="E23" s="164"/>
+      <c r="F23" s="165"/>
+      <c r="G23" s="91" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
+        <v>2</v>
+      </c>
+      <c r="C24" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="108"/>
+      <c r="E24" s="108"/>
+      <c r="F24" s="109"/>
+      <c r="G24" s="87" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
+        <v>3</v>
+      </c>
+      <c r="C25" s="175" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="176"/>
+      <c r="E25" s="176"/>
+      <c r="F25" s="177"/>
+      <c r="G25" s="89" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
         <v>4</v>
       </c>
-      <c r="C13" s="101" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="102"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="103"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28">
+      <c r="C26" s="166"/>
+      <c r="D26" s="167"/>
+      <c r="E26" s="167"/>
+      <c r="F26" s="168"/>
+      <c r="G26" s="87"/>
+    </row>
+    <row r="27" spans="1:21" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="32"/>
+      <c r="B27" s="29">
         <v>5</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="112"/>
-    </row>
-    <row r="15" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="30">
+      <c r="C27" s="169" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="170"/>
+      <c r="E27" s="170"/>
+      <c r="F27" s="171"/>
+      <c r="G27" s="87" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="31">
         <v>1</v>
       </c>
-      <c r="C15" s="113" t="s">
-        <v>104</v>
-      </c>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="115"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
+      <c r="C28" s="104" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="106"/>
+      <c r="G28" s="93" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="26"/>
+      <c r="B29" s="25">
         <v>2</v>
       </c>
-      <c r="C16" s="116"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="F16" s="118"/>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="C29" s="119"/>
+      <c r="D29" s="120"/>
+      <c r="E29" s="120"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="83"/>
+    </row>
+    <row r="30" spans="1:21" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="35"/>
+      <c r="B30" s="27">
         <v>3</v>
       </c>
-      <c r="C17" s="119" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="120"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="121"/>
-    </row>
-    <row r="18" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="31"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="123"/>
-      <c r="E18" s="123"/>
-      <c r="F18" s="124"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A19" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="30">
+      <c r="C30" s="113" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="114"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="115"/>
+      <c r="G30" s="87" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="35"/>
+      <c r="B31" s="27">
+        <v>4</v>
+      </c>
+      <c r="C31" s="119"/>
+      <c r="D31" s="120"/>
+      <c r="E31" s="120"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="87"/>
+      <c r="U31" s="67"/>
+    </row>
+    <row r="32" spans="1:21" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="36"/>
+      <c r="B32" s="37">
+        <v>5</v>
+      </c>
+      <c r="C32" s="122"/>
+      <c r="D32" s="123"/>
+      <c r="E32" s="123"/>
+      <c r="F32" s="124"/>
+      <c r="G32" s="85"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="31">
         <v>1</v>
       </c>
-      <c r="C19" s="98" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="99"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="100"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
-        <v>2</v>
-      </c>
-      <c r="C20" s="73"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="75"/>
-    </row>
-    <row r="21" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
+      <c r="C33" s="116" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="117"/>
+      <c r="E33" s="117"/>
+      <c r="F33" s="118"/>
+      <c r="G33" s="93" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="39"/>
+      <c r="B34" s="27">
         <v>3</v>
       </c>
-      <c r="C21" s="76" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="78"/>
-    </row>
-    <row r="22" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="31"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="88"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="89"/>
-      <c r="F22" s="90"/>
-    </row>
-    <row r="23" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="30">
-        <v>1</v>
-      </c>
-      <c r="C23" s="79" t="s">
+      <c r="C34" s="113" t="s">
+        <v>139</v>
+      </c>
+      <c r="D34" s="114"/>
+      <c r="E34" s="114"/>
+      <c r="F34" s="115"/>
+      <c r="G34" s="100" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="40"/>
+      <c r="B35" s="34">
+        <v>4</v>
+      </c>
+      <c r="C35" s="113" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="114"/>
+      <c r="E35" s="114" t="s">
+        <v>119</v>
+      </c>
+      <c r="F35" s="115"/>
+      <c r="G35" s="87" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="41"/>
+      <c r="B36" s="29">
+        <v>5</v>
+      </c>
+      <c r="C36" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="155"/>
+      <c r="E36" s="155"/>
+      <c r="F36" s="156"/>
+      <c r="G36" s="85" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="42"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="110"/>
+      <c r="D37" s="111"/>
+      <c r="E37" s="111"/>
+      <c r="F37" s="112"/>
+      <c r="G37" s="44"/>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="45"/>
+      <c r="B38" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="125" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="81"/>
-    </row>
-    <row r="24" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
-        <v>2</v>
-      </c>
-      <c r="C24" s="94" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="95"/>
-      <c r="E24" s="95"/>
-      <c r="F24" s="96"/>
-    </row>
-    <row r="25" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
-        <v>3</v>
-      </c>
-      <c r="C25" s="91" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92"/>
-      <c r="F25" s="93"/>
-    </row>
-    <row r="26" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26">
-        <v>4</v>
-      </c>
-      <c r="C26" s="82"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="84"/>
-    </row>
-    <row r="27" spans="1:20" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="31"/>
-      <c r="B27" s="28">
-        <v>5</v>
-      </c>
-      <c r="C27" s="85" t="s">
+      <c r="D38" s="126"/>
+      <c r="E38" s="126"/>
+      <c r="F38" s="127"/>
+      <c r="G38" s="94" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="47"/>
+      <c r="B39" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="86"/>
-      <c r="E27" s="86"/>
-      <c r="F27" s="87"/>
-    </row>
-    <row r="28" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="30">
-        <v>1</v>
-      </c>
-      <c r="C28" s="128" t="s">
-        <v>105</v>
-      </c>
-      <c r="D28" s="129"/>
-      <c r="E28" s="129"/>
-      <c r="F28" s="130"/>
-    </row>
-    <row r="29" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="25"/>
-      <c r="B29" s="24">
-        <v>2</v>
-      </c>
-      <c r="C29" s="138"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="140"/>
-    </row>
-    <row r="30" spans="1:20" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="34"/>
-      <c r="B30" s="26">
-        <v>3</v>
-      </c>
-      <c r="C30" s="134" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="135"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="136"/>
-    </row>
-    <row r="31" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="34"/>
-      <c r="B31" s="26">
-        <v>4</v>
-      </c>
-      <c r="C31" s="138"/>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="140"/>
-      <c r="T31" s="59"/>
-    </row>
-    <row r="32" spans="1:20" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="35"/>
-      <c r="B32" s="36">
-        <v>5</v>
-      </c>
-      <c r="C32" s="141"/>
-      <c r="D32" s="142"/>
-      <c r="E32" s="142"/>
-      <c r="F32" s="143"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="30">
-        <v>1</v>
-      </c>
-      <c r="C33" s="137" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="99"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="100"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="38"/>
-      <c r="B34" s="26">
-        <v>3</v>
-      </c>
-      <c r="C34" s="134" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34" s="135"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="136"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="39"/>
-      <c r="B35" s="33">
-        <v>4</v>
-      </c>
-      <c r="C35" s="134" t="s">
-        <v>83</v>
-      </c>
-      <c r="D35" s="135"/>
-      <c r="E35" s="135" t="s">
-        <v>84</v>
-      </c>
-      <c r="F35" s="136"/>
-    </row>
-    <row r="36" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="40"/>
-      <c r="B36" s="28">
-        <v>5</v>
-      </c>
-      <c r="C36" s="147" t="s">
-        <v>103</v>
-      </c>
-      <c r="D36" s="148"/>
-      <c r="E36" s="148"/>
-      <c r="F36" s="149"/>
-    </row>
-    <row r="37" spans="1:6" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="41"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="131"/>
-      <c r="D37" s="132"/>
-      <c r="E37" s="132"/>
-      <c r="F37" s="133"/>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="43"/>
-      <c r="B38" s="30" t="s">
+      <c r="C39" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="C38" s="144" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" s="145"/>
-      <c r="E38" s="145"/>
-      <c r="F38" s="146"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A39" s="44"/>
-      <c r="B39" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="94" t="s">
-        <v>31</v>
-      </c>
-      <c r="D39" s="95"/>
-      <c r="E39" s="95"/>
-      <c r="F39" s="96"/>
-    </row>
-    <row r="40" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="46"/>
-      <c r="B40" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="125" t="s">
-        <v>54</v>
-      </c>
-      <c r="D40" s="126"/>
-      <c r="E40" s="126"/>
-      <c r="F40" s="127"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="D39" s="108"/>
+      <c r="E39" s="108"/>
+      <c r="F39" s="109"/>
+      <c r="G39" s="86" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="49"/>
+      <c r="B40" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="101" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" s="102"/>
+      <c r="E40" s="102"/>
+      <c r="F40" s="103"/>
+      <c r="G40" s="84" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B42" s="2" t="s">
         <v>14</v>
       </c>
@@ -2661,16 +2930,35 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C39:F39"/>
@@ -2685,25 +2973,6 @@
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C24:F24"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2734,7 +3003,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2743,10 +3012,11 @@
     <col min="4" max="4" width="16.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="21" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -2754,15 +3024,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -2770,39 +3040,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="47" t="s">
-        <v>17</v>
+      <c r="C6" s="51" t="s">
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2812,401 +3082,465 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="52" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="97" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="97"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="128" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="128"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="49" t="s">
+      <c r="C9" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="52"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A10" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="24">
+      <c r="D9" s="54"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="25">
         <v>1</v>
       </c>
-      <c r="C10" s="153" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="154"/>
-      <c r="E10" s="154"/>
-      <c r="F10" s="155"/>
-    </row>
-    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="C10" s="219" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" s="220"/>
+      <c r="E10" s="220"/>
+      <c r="F10" s="221"/>
+      <c r="G10" s="87" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <v>2</v>
       </c>
-      <c r="C11" s="156" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
-      <c r="F11" s="158"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C11" s="222" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="223"/>
+      <c r="E11" s="223"/>
+      <c r="F11" s="224"/>
+      <c r="G11" s="88" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="162" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="168"/>
-      <c r="E12" s="169" t="s">
-        <v>87</v>
-      </c>
-      <c r="F12" s="164"/>
-    </row>
-    <row r="13" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
+      <c r="C12" s="195" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="231"/>
+      <c r="E12" s="232" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12" s="197"/>
+      <c r="G12" s="87" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29">
         <v>4</v>
       </c>
-      <c r="C13" s="159"/>
-      <c r="D13" s="160"/>
-      <c r="E13" s="160"/>
-      <c r="F13" s="161"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="30">
+      <c r="C13" s="225"/>
+      <c r="D13" s="226"/>
+      <c r="E13" s="226"/>
+      <c r="F13" s="227"/>
+      <c r="G13" s="50"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="31">
         <v>1</v>
       </c>
-      <c r="C14" s="165" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="166"/>
-      <c r="E14" s="166"/>
-      <c r="F14" s="167"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26">
+      <c r="C14" s="228" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="229"/>
+      <c r="E14" s="229"/>
+      <c r="F14" s="230"/>
+      <c r="G14" s="87" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27">
         <v>2</v>
       </c>
-      <c r="C15" s="162" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" s="163"/>
-      <c r="E15" s="163"/>
-      <c r="F15" s="164"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
+      <c r="C15" s="195" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="196"/>
+      <c r="E15" s="196"/>
+      <c r="F15" s="197"/>
+      <c r="G15" s="88" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
         <v>3</v>
       </c>
-      <c r="C16" s="138"/>
-      <c r="D16" s="139"/>
-      <c r="E16" s="139"/>
-      <c r="F16" s="140"/>
-    </row>
-    <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="C16" s="119"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="82"/>
+    </row>
+    <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
         <v>4</v>
       </c>
-      <c r="C17" s="162" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="163"/>
-      <c r="E17" s="163"/>
-      <c r="F17" s="164"/>
-    </row>
-    <row r="18" spans="1:9" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="31"/>
-      <c r="B18" s="28">
+      <c r="C17" s="195" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="196"/>
+      <c r="E17" s="196"/>
+      <c r="F17" s="197"/>
+      <c r="G17" s="87" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="32"/>
+      <c r="B18" s="29">
         <v>5</v>
       </c>
-      <c r="C18" s="150"/>
-      <c r="D18" s="151"/>
-      <c r="E18" s="151"/>
-      <c r="F18" s="152"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A19" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="30">
+      <c r="C18" s="216"/>
+      <c r="D18" s="217"/>
+      <c r="E18" s="217"/>
+      <c r="F18" s="218"/>
+      <c r="G18" s="50"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A19" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="31">
         <v>1</v>
       </c>
-      <c r="C19" s="173"/>
-      <c r="D19" s="174"/>
-      <c r="E19" s="174"/>
-      <c r="F19" s="175"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
+      <c r="C19" s="204"/>
+      <c r="D19" s="205"/>
+      <c r="E19" s="205"/>
+      <c r="F19" s="206"/>
+      <c r="G19" s="66"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
         <v>2</v>
       </c>
-      <c r="C20" s="176" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="177"/>
-      <c r="E20" s="177"/>
-      <c r="F20" s="178"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
+      <c r="C20" s="207" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="208"/>
+      <c r="E20" s="208"/>
+      <c r="F20" s="209"/>
+      <c r="G20" s="87" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <v>3</v>
       </c>
-      <c r="C21" s="179"/>
-      <c r="D21" s="180"/>
-      <c r="E21" s="180"/>
-      <c r="F21" s="181"/>
-    </row>
-    <row r="22" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
+      <c r="C21" s="210"/>
+      <c r="D21" s="211"/>
+      <c r="E21" s="211"/>
+      <c r="F21" s="212"/>
+      <c r="G21" s="82"/>
+    </row>
+    <row r="22" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
         <v>4</v>
       </c>
-      <c r="C22" s="179"/>
-      <c r="D22" s="180"/>
-      <c r="E22" s="180"/>
-      <c r="F22" s="181"/>
-    </row>
-    <row r="23" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="31"/>
-      <c r="B23" s="28">
+      <c r="C22" s="210"/>
+      <c r="D22" s="211"/>
+      <c r="E22" s="211"/>
+      <c r="F22" s="212"/>
+      <c r="G22" s="82"/>
+    </row>
+    <row r="23" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="32"/>
+      <c r="B23" s="29">
         <v>5</v>
       </c>
-      <c r="C23" s="88"/>
-      <c r="D23" s="89"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="90"/>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="30">
+      <c r="C23" s="172"/>
+      <c r="D23" s="173"/>
+      <c r="E23" s="173"/>
+      <c r="F23" s="174"/>
+      <c r="G23" s="81"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="31">
         <v>3</v>
       </c>
-      <c r="C24" s="182"/>
-      <c r="D24" s="183"/>
-      <c r="E24" s="183"/>
-      <c r="F24" s="184"/>
-    </row>
-    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
+      <c r="C24" s="213"/>
+      <c r="D24" s="214"/>
+      <c r="E24" s="214"/>
+      <c r="F24" s="215"/>
+      <c r="G24" s="66"/>
+    </row>
+    <row r="25" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
         <v>4</v>
       </c>
-      <c r="C25" s="94" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" s="95"/>
-      <c r="E25" s="95"/>
-      <c r="F25" s="96"/>
-      <c r="I25" s="53"/>
-    </row>
-    <row r="26" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26">
+      <c r="C25" s="107" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="108"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="109"/>
+      <c r="G25" s="88" t="s">
+        <v>45</v>
+      </c>
+      <c r="J25" s="58"/>
+    </row>
+    <row r="26" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
         <v>5</v>
       </c>
-      <c r="C26" s="138"/>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="140"/>
-    </row>
-    <row r="27" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="32"/>
-      <c r="B27" s="33">
+      <c r="C26" s="119"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="120"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="82"/>
+    </row>
+    <row r="27" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="33"/>
+      <c r="B27" s="34">
         <v>6</v>
       </c>
-      <c r="C27" s="162" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="163"/>
-      <c r="E27" s="163"/>
-      <c r="F27" s="164"/>
-    </row>
-    <row r="28" spans="1:9" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="31"/>
-      <c r="B28" s="28">
+      <c r="C27" s="195" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" s="196"/>
+      <c r="E27" s="196"/>
+      <c r="F27" s="197"/>
+      <c r="G27" s="88" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="32"/>
+      <c r="B28" s="29">
         <v>7</v>
       </c>
-      <c r="C28" s="170"/>
-      <c r="D28" s="171"/>
-      <c r="E28" s="171"/>
-      <c r="F28" s="172"/>
-      <c r="I28" s="53"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A29" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="30">
+      <c r="C28" s="201"/>
+      <c r="D28" s="202"/>
+      <c r="E28" s="202"/>
+      <c r="F28" s="203"/>
+      <c r="G28" s="50"/>
+      <c r="J28" s="58"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A29" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="31">
         <v>3</v>
       </c>
-      <c r="C29" s="98" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" s="188"/>
-      <c r="E29" s="188"/>
-      <c r="F29" s="189"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A30" s="34"/>
-      <c r="B30" s="26">
+      <c r="C29" s="129" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="181"/>
+      <c r="E29" s="181"/>
+      <c r="F29" s="182"/>
+      <c r="G29" s="90" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A30" s="35"/>
+      <c r="B30" s="27">
         <v>4</v>
       </c>
-      <c r="C30" s="162" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="163"/>
-      <c r="E30" s="163"/>
-      <c r="F30" s="164"/>
-    </row>
-    <row r="31" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="34"/>
-      <c r="B31" s="26">
+      <c r="C30" s="195" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="196"/>
+      <c r="E30" s="196"/>
+      <c r="F30" s="197"/>
+      <c r="G30" s="87" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="35"/>
+      <c r="B31" s="27">
         <v>5</v>
       </c>
-      <c r="C31" s="202"/>
-      <c r="D31" s="203"/>
-      <c r="E31" s="203"/>
-      <c r="F31" s="204"/>
-    </row>
-    <row r="32" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="54"/>
-      <c r="B32" s="28">
+      <c r="C31" s="198"/>
+      <c r="D31" s="199"/>
+      <c r="E31" s="199"/>
+      <c r="F31" s="200"/>
+      <c r="G31" s="87"/>
+    </row>
+    <row r="32" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="59"/>
+      <c r="B32" s="29">
         <v>6</v>
       </c>
-      <c r="C32" s="190"/>
-      <c r="D32" s="191"/>
-      <c r="E32" s="191"/>
-      <c r="F32" s="192"/>
-    </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="71" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="60">
+      <c r="C32" s="183"/>
+      <c r="D32" s="184"/>
+      <c r="E32" s="184"/>
+      <c r="F32" s="185"/>
+      <c r="G32" s="81"/>
+    </row>
+    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="79" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="68">
         <v>1</v>
       </c>
-      <c r="C33" s="193"/>
-      <c r="D33" s="194"/>
-      <c r="E33" s="194"/>
-      <c r="F33" s="195"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="61"/>
-      <c r="B34" s="68">
+      <c r="C33" s="186"/>
+      <c r="D33" s="187"/>
+      <c r="E33" s="187"/>
+      <c r="F33" s="188"/>
+      <c r="G33" s="46"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="69"/>
+      <c r="B34" s="76">
         <v>2</v>
       </c>
-      <c r="C34" s="199"/>
-      <c r="D34" s="200"/>
-      <c r="E34" s="200"/>
-      <c r="F34" s="201"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="61"/>
-      <c r="B35" s="68">
+      <c r="C34" s="192"/>
+      <c r="D34" s="193"/>
+      <c r="E34" s="193"/>
+      <c r="F34" s="194"/>
+      <c r="G34" s="57"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="69"/>
+      <c r="B35" s="76">
         <v>3</v>
       </c>
-      <c r="C35" s="199"/>
-      <c r="D35" s="200"/>
-      <c r="E35" s="200"/>
-      <c r="F35" s="201"/>
-    </row>
-    <row r="36" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="72"/>
-      <c r="B36" s="69">
+      <c r="C35" s="192"/>
+      <c r="D35" s="193"/>
+      <c r="E35" s="193"/>
+      <c r="F35" s="194"/>
+      <c r="G35" s="57"/>
+    </row>
+    <row r="36" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="80"/>
+      <c r="B36" s="77">
         <v>4</v>
       </c>
-      <c r="C36" s="125" t="s">
+      <c r="C36" s="101" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="102"/>
+      <c r="E36" s="102"/>
+      <c r="F36" s="103"/>
+      <c r="G36" s="85" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="78"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="189"/>
+      <c r="D37" s="190"/>
+      <c r="E37" s="190"/>
+      <c r="F37" s="191"/>
+      <c r="G37" s="60"/>
+    </row>
+    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="70"/>
+      <c r="B38" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="127"/>
-    </row>
-    <row r="37" spans="1:6" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="70"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="196"/>
-      <c r="D37" s="197"/>
-      <c r="E37" s="197"/>
-      <c r="F37" s="198"/>
-    </row>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="62"/>
-      <c r="B38" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="128" t="s">
-        <v>38</v>
-      </c>
-      <c r="D38" s="129"/>
-      <c r="E38" s="129"/>
-      <c r="F38" s="130"/>
-    </row>
-    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="63"/>
-      <c r="B39" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="162" t="s">
-        <v>58</v>
-      </c>
-      <c r="D39" s="163"/>
-      <c r="E39" s="163"/>
-      <c r="F39" s="164"/>
-    </row>
-    <row r="40" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="64"/>
-      <c r="B40" s="67" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="185" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" s="186"/>
-      <c r="E40" s="186"/>
-      <c r="F40" s="187"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C38" s="104" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="105"/>
+      <c r="E38" s="105"/>
+      <c r="F38" s="106"/>
+      <c r="G38" s="94" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="71"/>
+      <c r="B39" s="74" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="195" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" s="196"/>
+      <c r="E39" s="196"/>
+      <c r="F39" s="197"/>
+      <c r="G39" s="88" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="72"/>
+      <c r="B40" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" s="178" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="179"/>
+      <c r="E40" s="179"/>
+      <c r="F40" s="180"/>
+      <c r="G40" s="84" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B42" s="2" t="s">
         <v>14</v>
       </c>
@@ -3214,16 +3548,37 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C23:F23"/>
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C32:F32"/>
@@ -3236,27 +3591,6 @@
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3287,7 +3621,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3295,10 +3629,11 @@
     <col min="3" max="3" width="20" style="2" customWidth="1"/>
     <col min="4" max="5" width="16.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="22" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3306,15 +3641,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3322,39 +3657,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="47" t="s">
-        <v>17</v>
+      <c r="C6" s="51" t="s">
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3364,35 +3699,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="52" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="97" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="97"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="128" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="128"/>
+      <c r="E8" s="128"/>
+      <c r="F8" s="128"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>0</v>
@@ -3403,290 +3738,347 @@
       <c r="D9" s="20"/>
       <c r="E9" s="21"/>
       <c r="F9" s="22"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="30">
+      <c r="G9" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="31">
         <v>1</v>
       </c>
-      <c r="C10" s="226" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="227"/>
-      <c r="E10" s="227"/>
-      <c r="F10" s="228"/>
-    </row>
-    <row r="11" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="C10" s="269" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="270"/>
+      <c r="E10" s="270"/>
+      <c r="F10" s="271"/>
+      <c r="G10" s="93" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <v>2</v>
       </c>
-      <c r="C11" s="205" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="206"/>
-      <c r="E11" s="206"/>
-      <c r="F11" s="207"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C11" s="236" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="237"/>
+      <c r="E11" s="237"/>
+      <c r="F11" s="238"/>
+      <c r="G11" s="87" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="82"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="84"/>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="27"/>
-      <c r="B13" s="28">
+      <c r="C12" s="166"/>
+      <c r="D12" s="167"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="168"/>
+      <c r="G12" s="87"/>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="28"/>
+      <c r="B13" s="29">
         <v>4</v>
       </c>
-      <c r="C13" s="208"/>
-      <c r="D13" s="209"/>
-      <c r="E13" s="209"/>
-      <c r="F13" s="210"/>
-    </row>
-    <row r="14" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="30">
+      <c r="C13" s="251"/>
+      <c r="D13" s="252"/>
+      <c r="E13" s="252"/>
+      <c r="F13" s="253"/>
+      <c r="G13" s="81"/>
+    </row>
+    <row r="14" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="31">
         <v>1</v>
       </c>
-      <c r="C14" s="229" t="s">
+      <c r="C14" s="272" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="273"/>
+      <c r="E14" s="273"/>
+      <c r="F14" s="274"/>
+      <c r="G14" s="93" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27">
+        <v>2</v>
+      </c>
+      <c r="C15" s="263" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="264"/>
+      <c r="E15" s="264"/>
+      <c r="F15" s="265"/>
+      <c r="G15" s="87" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>3</v>
+      </c>
+      <c r="C16" s="266" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="267"/>
+      <c r="E16" s="267"/>
+      <c r="F16" s="268"/>
+      <c r="G16" s="87" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="32"/>
+      <c r="B17" s="29">
+        <v>4</v>
+      </c>
+      <c r="C17" s="257"/>
+      <c r="D17" s="258"/>
+      <c r="E17" s="258"/>
+      <c r="F17" s="259"/>
+      <c r="G17" s="81"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="31">
+        <v>1</v>
+      </c>
+      <c r="C18" s="186"/>
+      <c r="D18" s="187"/>
+      <c r="E18" s="187"/>
+      <c r="F18" s="188"/>
+      <c r="G18" s="46"/>
+    </row>
+    <row r="19" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="26"/>
+      <c r="B19" s="27">
+        <v>2</v>
+      </c>
+      <c r="C19" s="260" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="261"/>
+      <c r="E19" s="261"/>
+      <c r="F19" s="262"/>
+      <c r="G19" s="88" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="230"/>
-      <c r="E14" s="230"/>
-      <c r="F14" s="231"/>
-    </row>
-    <row r="15" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26">
+    </row>
+    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
+        <v>3</v>
+      </c>
+      <c r="C20" s="254" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="255"/>
+      <c r="E20" s="255"/>
+      <c r="F20" s="256"/>
+      <c r="G20" s="87" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="32"/>
+      <c r="B21" s="29">
+        <v>4</v>
+      </c>
+      <c r="C21" s="151"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
+      <c r="F21" s="153"/>
+      <c r="G21" s="50"/>
+    </row>
+    <row r="22" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="31">
+        <v>1</v>
+      </c>
+      <c r="C22" s="275"/>
+      <c r="D22" s="276"/>
+      <c r="E22" s="276"/>
+      <c r="F22" s="277"/>
+      <c r="G22" s="66"/>
+    </row>
+    <row r="23" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27">
         <v>2</v>
       </c>
-      <c r="C15" s="220" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="221"/>
-      <c r="E15" s="221"/>
-      <c r="F15" s="222"/>
-    </row>
-    <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
+      <c r="C23" s="260" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" s="261"/>
+      <c r="E23" s="261"/>
+      <c r="F23" s="262"/>
+      <c r="G23" s="87" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
         <v>3</v>
       </c>
-      <c r="C16" s="223" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="224"/>
-      <c r="E16" s="224"/>
-      <c r="F16" s="225"/>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="31"/>
-      <c r="B17" s="28">
+      <c r="C24" s="254" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="255"/>
+      <c r="E24" s="255"/>
+      <c r="F24" s="256"/>
+      <c r="G24" s="87" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="32"/>
+      <c r="B25" s="29">
         <v>4</v>
       </c>
-      <c r="C17" s="214"/>
-      <c r="D17" s="215"/>
-      <c r="E17" s="215"/>
-      <c r="F17" s="216"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="30">
+      <c r="C25" s="233"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="234"/>
+      <c r="F25" s="235"/>
+      <c r="G25" s="87"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="31">
         <v>1</v>
       </c>
-      <c r="C18" s="193"/>
-      <c r="D18" s="194"/>
-      <c r="E18" s="194"/>
-      <c r="F18" s="195"/>
-    </row>
-    <row r="19" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="25"/>
-      <c r="B19" s="26">
+      <c r="C26" s="248" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="249"/>
+      <c r="E26" s="249"/>
+      <c r="F26" s="250"/>
+      <c r="G26" s="99" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="35"/>
+      <c r="B27" s="27">
         <v>2</v>
       </c>
-      <c r="C19" s="217" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="218"/>
-      <c r="E19" s="218"/>
-      <c r="F19" s="219"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
+      <c r="C27" s="245" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="246"/>
+      <c r="E27" s="246"/>
+      <c r="F27" s="247"/>
+      <c r="G27" s="98" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="35"/>
+      <c r="B28" s="27">
         <v>3</v>
       </c>
-      <c r="C20" s="211" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="212"/>
-      <c r="E20" s="212"/>
-      <c r="F20" s="213"/>
-    </row>
-    <row r="21" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="31"/>
-      <c r="B21" s="28">
+      <c r="C28" s="236" t="s">
+        <v>131</v>
+      </c>
+      <c r="D28" s="237"/>
+      <c r="E28" s="237"/>
+      <c r="F28" s="238"/>
+      <c r="G28" s="87" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="59"/>
+      <c r="B29" s="29">
         <v>4</v>
       </c>
-      <c r="C21" s="122"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="123"/>
-      <c r="F21" s="124"/>
-    </row>
-    <row r="22" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="30">
+      <c r="C29" s="239" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="240"/>
+      <c r="E29" s="240"/>
+      <c r="F29" s="241"/>
+      <c r="G29" s="89" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="31">
         <v>1</v>
       </c>
-      <c r="C22" s="232"/>
-      <c r="D22" s="233"/>
-      <c r="E22" s="233"/>
-      <c r="F22" s="234"/>
-    </row>
-    <row r="23" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26">
+      <c r="C30" s="242"/>
+      <c r="D30" s="243"/>
+      <c r="E30" s="243"/>
+      <c r="F30" s="244"/>
+      <c r="G30" s="46"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="39"/>
+      <c r="B31" s="27">
         <v>2</v>
       </c>
-      <c r="C23" s="217" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" s="218"/>
-      <c r="E23" s="218"/>
-      <c r="F23" s="219"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
+      <c r="C31" s="157"/>
+      <c r="D31" s="158"/>
+      <c r="E31" s="158"/>
+      <c r="F31" s="159"/>
+      <c r="G31" s="57"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="39"/>
+      <c r="B32" s="27">
         <v>3</v>
       </c>
-      <c r="C24" s="211" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="212"/>
-      <c r="E24" s="212"/>
-      <c r="F24" s="213"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="31"/>
-      <c r="B25" s="28">
+      <c r="C32" s="207" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="208"/>
+      <c r="E32" s="208"/>
+      <c r="F32" s="209"/>
+      <c r="G32" s="88" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="41"/>
+      <c r="B33" s="29">
         <v>4</v>
       </c>
-      <c r="C25" s="235"/>
-      <c r="D25" s="236"/>
-      <c r="E25" s="236"/>
-      <c r="F25" s="237"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="30">
-        <v>1</v>
-      </c>
-      <c r="C26" s="247" t="s">
-        <v>102</v>
-      </c>
-      <c r="D26" s="248"/>
-      <c r="E26" s="248"/>
-      <c r="F26" s="249"/>
-    </row>
-    <row r="27" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="34"/>
-      <c r="B27" s="26">
-        <v>2</v>
-      </c>
-      <c r="C27" s="244" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="245"/>
-      <c r="E27" s="245"/>
-      <c r="F27" s="246"/>
-    </row>
-    <row r="28" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="34"/>
-      <c r="B28" s="26">
-        <v>3</v>
-      </c>
-      <c r="C28" s="205" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" s="206"/>
-      <c r="E28" s="206"/>
-      <c r="F28" s="207"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="54"/>
-      <c r="B29" s="28">
-        <v>4</v>
-      </c>
-      <c r="C29" s="238" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="239"/>
-      <c r="E29" s="239"/>
-      <c r="F29" s="240"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="30">
-        <v>1</v>
-      </c>
-      <c r="C30" s="241"/>
-      <c r="D30" s="242"/>
-      <c r="E30" s="242"/>
-      <c r="F30" s="243"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="38"/>
-      <c r="B31" s="26">
-        <v>2</v>
-      </c>
-      <c r="C31" s="73"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="75"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="38"/>
-      <c r="B32" s="26">
-        <v>3</v>
-      </c>
-      <c r="C32" s="176" t="s">
-        <v>40</v>
-      </c>
-      <c r="D32" s="177"/>
-      <c r="E32" s="177"/>
-      <c r="F32" s="178"/>
-    </row>
-    <row r="33" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="40"/>
-      <c r="B33" s="28">
-        <v>4</v>
-      </c>
-      <c r="C33" s="147" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="148"/>
-      <c r="E33" s="148"/>
-      <c r="F33" s="149"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C33" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="155"/>
+      <c r="E33" s="155"/>
+      <c r="F33" s="156"/>
+      <c r="G33" s="84" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B35" s="2" t="s">
         <v>14</v>
       </c>
@@ -3694,25 +4086,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C32:F32"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C13:F13"/>
@@ -3729,6 +4112,15 @@
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C32:F32"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -3759,7 +4151,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3768,10 +4160,11 @@
     <col min="4" max="4" width="18.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="18" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -3779,15 +4172,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -3795,39 +4188,39 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="47" t="s">
-        <v>17</v>
+      <c r="C6" s="51" t="s">
+        <v>18</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3837,44 +4230,44 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="48" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="52" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="15" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="57"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="65"/>
+      <c r="E8" s="64"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="97" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="97"/>
-      <c r="E9" s="57"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+      <c r="C9" s="128" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" s="128"/>
+      <c r="E9" s="64"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>0</v>
@@ -3885,296 +4278,348 @@
       <c r="D10" s="20"/>
       <c r="E10" s="21"/>
       <c r="F10" s="22"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="24">
+      <c r="G10" s="23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="265"/>
-      <c r="D11" s="266"/>
-      <c r="E11" s="266"/>
-      <c r="F11" s="267"/>
-    </row>
-    <row r="12" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C11" s="281"/>
+      <c r="D11" s="282"/>
+      <c r="E11" s="282"/>
+      <c r="F11" s="283"/>
+      <c r="G11" s="66"/>
+    </row>
+    <row r="12" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="244" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" s="245"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="84"/>
-    </row>
-    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="C12" s="245" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="246"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="168"/>
+      <c r="G12" s="87" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
         <v>4</v>
       </c>
-      <c r="C13" s="244" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="245"/>
-      <c r="E13" s="245"/>
-      <c r="F13" s="246"/>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
+      <c r="C13" s="245" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="246"/>
+      <c r="E13" s="246"/>
+      <c r="F13" s="247"/>
+      <c r="G13" s="87" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
         <v>5</v>
       </c>
-      <c r="C14" s="268" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="269"/>
-      <c r="E14" s="269"/>
-      <c r="F14" s="270"/>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="27"/>
-      <c r="B15" s="28">
+      <c r="C14" s="284" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="285"/>
+      <c r="E14" s="285"/>
+      <c r="F14" s="286"/>
+      <c r="G14" s="87" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29">
         <v>6</v>
       </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="112"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="30">
+      <c r="C15" s="139"/>
+      <c r="D15" s="140"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="81"/>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="31">
         <v>1</v>
       </c>
-      <c r="C16" s="113" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
-      <c r="F16" s="115"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="C16" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="96" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
         <v>2</v>
       </c>
-      <c r="C17" s="264" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" s="250"/>
-      <c r="E17" s="250"/>
-      <c r="F17" s="251"/>
-    </row>
-    <row r="18" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26">
+      <c r="C17" s="278" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" s="279"/>
+      <c r="E17" s="279"/>
+      <c r="F17" s="280"/>
+      <c r="G17" s="97" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27">
         <v>3</v>
       </c>
-      <c r="C18" s="271"/>
-      <c r="D18" s="272"/>
-      <c r="E18" s="250" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="251"/>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="31"/>
-      <c r="B19" s="28">
+      <c r="C18" s="290"/>
+      <c r="D18" s="291"/>
+      <c r="E18" s="279" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" s="280"/>
+      <c r="G18" s="97" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="32"/>
+      <c r="B19" s="29">
         <v>4</v>
       </c>
-      <c r="C19" s="214"/>
-      <c r="D19" s="215"/>
-      <c r="E19" s="215"/>
-      <c r="F19" s="216"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="30">
+      <c r="C19" s="257"/>
+      <c r="D19" s="258"/>
+      <c r="E19" s="258"/>
+      <c r="F19" s="259"/>
+      <c r="G19" s="95"/>
+    </row>
+    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="31">
         <v>1</v>
       </c>
-      <c r="C20" s="79" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="81"/>
-    </row>
-    <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
+      <c r="C20" s="163" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="164"/>
+      <c r="E20" s="164"/>
+      <c r="F20" s="165"/>
+      <c r="G20" s="93" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <v>2</v>
       </c>
-      <c r="C21" s="134" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="135"/>
-      <c r="E21" s="135"/>
-      <c r="F21" s="136"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
+      <c r="C21" s="113" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="87" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
         <v>3</v>
       </c>
-      <c r="C22" s="162" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="163"/>
-      <c r="E22" s="163"/>
-      <c r="F22" s="164"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="31"/>
-      <c r="B23" s="28">
+      <c r="C22" s="195" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" s="196"/>
+      <c r="E22" s="196"/>
+      <c r="F22" s="197"/>
+      <c r="G22" s="88" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="32"/>
+      <c r="B23" s="29">
         <v>4</v>
       </c>
-      <c r="C23" s="208"/>
-      <c r="D23" s="209"/>
-      <c r="E23" s="209"/>
-      <c r="F23" s="210"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="30">
+      <c r="C23" s="251"/>
+      <c r="D23" s="252"/>
+      <c r="E23" s="252"/>
+      <c r="F23" s="253"/>
+      <c r="G23" s="81"/>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="31">
         <v>1</v>
       </c>
-      <c r="C24" s="255" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="256"/>
-      <c r="E24" s="256"/>
-      <c r="F24" s="257"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
+      <c r="C24" s="287" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="288"/>
+      <c r="E24" s="288"/>
+      <c r="F24" s="289"/>
+      <c r="G24" s="93"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
         <v>2</v>
       </c>
-      <c r="C25" s="138"/>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="140"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26">
+      <c r="C25" s="119"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="120"/>
+      <c r="F25" s="121"/>
+      <c r="G25" s="88"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
         <v>3</v>
       </c>
-      <c r="C26" s="138"/>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="140"/>
-    </row>
-    <row r="27" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="31"/>
-      <c r="B27" s="28">
+      <c r="C26" s="119"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="120"/>
+      <c r="F26" s="121"/>
+      <c r="G26" s="57"/>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="32"/>
+      <c r="B27" s="29">
         <v>4</v>
       </c>
-      <c r="C27" s="122"/>
-      <c r="D27" s="123"/>
-      <c r="E27" s="123"/>
-      <c r="F27" s="124"/>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="30">
+      <c r="C27" s="151"/>
+      <c r="D27" s="152"/>
+      <c r="E27" s="152"/>
+      <c r="F27" s="153"/>
+      <c r="G27" s="50"/>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="31">
         <v>2</v>
       </c>
-      <c r="C28" s="258"/>
-      <c r="D28" s="259"/>
-      <c r="E28" s="259"/>
-      <c r="F28" s="260"/>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="34"/>
-      <c r="B29" s="26">
+      <c r="C28" s="295"/>
+      <c r="D28" s="296"/>
+      <c r="E28" s="296"/>
+      <c r="F28" s="297"/>
+      <c r="G28" s="96"/>
+    </row>
+    <row r="29" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="35"/>
+      <c r="B29" s="27">
         <v>3</v>
       </c>
-      <c r="C29" s="162" t="s">
-        <v>97</v>
-      </c>
-      <c r="D29" s="163"/>
-      <c r="E29" s="163"/>
-      <c r="F29" s="164"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="34"/>
-      <c r="B30" s="26">
+      <c r="C29" s="195" t="s">
+        <v>135</v>
+      </c>
+      <c r="D29" s="196"/>
+      <c r="E29" s="196"/>
+      <c r="F29" s="197"/>
+      <c r="G29" s="88" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="35"/>
+      <c r="B30" s="27">
         <v>4</v>
       </c>
-      <c r="C30" s="252" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="253"/>
-      <c r="E30" s="253"/>
-      <c r="F30" s="254"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="54"/>
-      <c r="B31" s="28">
+      <c r="C30" s="292" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="293"/>
+      <c r="E30" s="293"/>
+      <c r="F30" s="294"/>
+      <c r="G30" s="88" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="59"/>
+      <c r="B31" s="29">
         <v>5</v>
       </c>
-      <c r="C31" s="261" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="262"/>
-      <c r="E31" s="262"/>
-      <c r="F31" s="263"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="56" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="24">
+      <c r="C31" s="298" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="299"/>
+      <c r="E31" s="299"/>
+      <c r="F31" s="300"/>
+      <c r="G31" s="85" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="62" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="25">
         <v>1</v>
       </c>
-      <c r="C32" s="255" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" s="256"/>
-      <c r="E32" s="256"/>
-      <c r="F32" s="257"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="38"/>
-      <c r="B33" s="26">
+      <c r="C32" s="287" t="s">
+        <v>136</v>
+      </c>
+      <c r="D32" s="288"/>
+      <c r="E32" s="288"/>
+      <c r="F32" s="289"/>
+      <c r="G32" s="63"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="39"/>
+      <c r="B33" s="27">
         <v>2</v>
       </c>
-      <c r="C33" s="138"/>
-      <c r="D33" s="139"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="140"/>
-    </row>
-    <row r="34" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="38"/>
-      <c r="B34" s="26">
+      <c r="C33" s="119"/>
+      <c r="D33" s="120"/>
+      <c r="E33" s="120"/>
+      <c r="F33" s="121"/>
+      <c r="G33" s="57"/>
+    </row>
+    <row r="34" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="39"/>
+      <c r="B34" s="27">
         <v>3</v>
       </c>
-      <c r="C34" s="138"/>
-      <c r="D34" s="139"/>
-      <c r="E34" s="139"/>
-      <c r="F34" s="140"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="46"/>
-      <c r="B35" s="55"/>
-      <c r="C35" s="88"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="90"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C34" s="119"/>
+      <c r="D34" s="120"/>
+      <c r="E34" s="120"/>
+      <c r="F34" s="121"/>
+      <c r="G34" s="57"/>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="49"/>
+      <c r="B35" s="61"/>
+      <c r="C35" s="172"/>
+      <c r="D35" s="173"/>
+      <c r="E35" s="173"/>
+      <c r="F35" s="174"/>
+      <c r="G35" s="50"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B37" s="2" t="s">
         <v>14</v>
       </c>
@@ -4182,16 +4627,28 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C31:F31"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="C22:F22"/>
@@ -4208,18 +4665,6 @@
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C31:F31"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
